--- a/spanova_data/kesit şekilleri.xlsx
+++ b/spanova_data/kesit şekilleri.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_ZHarput_Data\SPANOVA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_ZHarput_Data\SPANOVA\spanova_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4745B4A-0788-4EDC-B455-9FBD56D88FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6652EB0-C5B8-41FC-8EA6-424353E0A51F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{05308F05-59E8-4F85-A725-5321E85E70C5}"/>
   </bookViews>
@@ -93,23 +93,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>58</xdr:col>
-      <xdr:colOff>74390</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>151206</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>38060</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>105752</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>516256</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>132250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46F3C872-EA30-FD6A-36E8-306F4AF93C40}"/>
+        <xdr:cNvPr id="37" name="Picture 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24FB7AA8-E16F-29F6-0EF0-1EB8E871EDB9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -124,9 +124,9 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20955000" y="885825"/>
-          <a:ext cx="14476190" cy="9552381"/>
+        <a:xfrm rot="5400000">
+          <a:off x="12286116" y="12730370"/>
+          <a:ext cx="4788998" cy="3542761"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -137,23 +137,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>133351</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>95251</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>180409</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>133351</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>58</xdr:col>
+      <xdr:colOff>74390</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>151206</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FD1E798-B596-C5FC-804E-605C9F03776A}"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46F3C872-EA30-FD6A-36E8-306F4AF93C40}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -169,8 +169,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6838951" y="285751"/>
-          <a:ext cx="3704658" cy="5562600"/>
+          <a:off x="20955000" y="885825"/>
+          <a:ext cx="14476190" cy="9552381"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -181,23 +181,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>155596</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>133351</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>565656</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>95251</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>180409</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CEC23A4-BBD1-4B4B-8CAB-825BE151EE9C}"/>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FD1E798-B596-C5FC-804E-605C9F03776A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -213,8 +213,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3203596" y="333375"/>
-          <a:ext cx="3458060" cy="5000625"/>
+          <a:off x="6838951" y="285751"/>
+          <a:ext cx="3704658" cy="5562600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -225,23 +225,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>228298</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>84588</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>155596</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>565656</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D96651B1-E795-0C85-1693-472F995F5DC5}"/>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CEC23A4-BBD1-4B4B-8CAB-825BE151EE9C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -257,8 +257,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="247650" y="133350"/>
-          <a:ext cx="2419048" cy="9095238"/>
+          <a:off x="3203596" y="333375"/>
+          <a:ext cx="3458060" cy="5000625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -269,23 +269,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>409654</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>225679</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>228298</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>84588</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C593CF8B-942D-8FB2-86EF-7E581EE874FE}"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D96651B1-E795-0C85-1693-472F995F5DC5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -301,8 +301,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10772854" y="447675"/>
-          <a:ext cx="3473625" cy="4648200"/>
+          <a:off x="247650" y="133350"/>
+          <a:ext cx="2419048" cy="9095238"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -313,23 +313,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>409654</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>460116</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>608859</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>122790</xdr:rowOff>
+      <xdr:colOff>225679</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A043A70-F6E4-7F6B-7695-53194E71C665}"/>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C593CF8B-942D-8FB2-86EF-7E581EE874FE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -345,8 +345,2642 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
+          <a:off x="10772854" y="447675"/>
+          <a:ext cx="3473625" cy="4648200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>460116</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>608859</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>122790</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A043A70-F6E4-7F6B-7695-53194E71C665}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="14480916" y="419100"/>
           <a:ext cx="3196743" cy="4466190"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Rectangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{495DC658-5F4A-4C54-2DE7-A3787F622F8C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8534400" y="7048500"/>
+          <a:ext cx="1219200" cy="2095500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="tr-TR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Rectangle 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6BFD5D1-6FCE-4436-BAD7-C17B37592A53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8801100" y="7267575"/>
+          <a:ext cx="695325" cy="1600200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="tr-TR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Rectangle 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C7247FB-DBE1-4FB4-BA4B-A7B5B74CC9C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10591800" y="7058025"/>
+          <a:ext cx="1219200" cy="2095500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="tr-TR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Rectangle 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66048F06-6C88-48BF-A25D-154BC4C28898}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10848975" y="7048499"/>
+          <a:ext cx="695325" cy="619125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="tr-TR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>173832</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>30957</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Rectangle 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A1A1E8D-629E-4A22-ADCE-DB61E970C521}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10808494" y="8555832"/>
+          <a:ext cx="692944" cy="619125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="tr-TR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>566737</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>13097</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>557213</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>79772</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Oval 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6C98DA1-4F05-B618-DAD4-3337BA6367A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6638925" y="7061597"/>
+          <a:ext cx="597694" cy="638175"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="tr-TR" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>29767</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>561976</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>96442</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Oval 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFF91B16-BFAC-4CE4-B420-1C342A439049}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6643688" y="8221267"/>
+          <a:ext cx="597694" cy="638175"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="tr-TR" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>565546</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>136921</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>565547</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>184547</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Rectangle 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F40513F5-3CBA-41DD-8B5B-E80977CEA8C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6637734" y="7375921"/>
+          <a:ext cx="607219" cy="1190626"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="tr-TR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>184547</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>583409</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>65484</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="22" name="Group 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD128AF5-17BC-766E-D739-01ECA2E1D0EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="10839450" y="7042547"/>
+          <a:ext cx="716759" cy="642937"/>
+          <a:chOff x="10798969" y="7042547"/>
+          <a:chExt cx="714378" cy="642937"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="18" name="Straight Connector 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{833F7644-88DD-9FCC-CF3C-6AC5D6252E81}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10798969" y="7042547"/>
+            <a:ext cx="0" cy="631031"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="19" name="Straight Connector 18">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB5934CB-768E-4B77-A716-0F3F47A97E0E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11507390" y="7054453"/>
+            <a:ext cx="0" cy="631031"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="20" name="Straight Connector 19">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE2C0C29-D835-48CD-AB37-78AA477F8E8C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10810875" y="7673579"/>
+            <a:ext cx="702472" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>470297</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>577456</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="23" name="Group 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{928A2BE4-596B-4C35-931E-844E1E0F7ECC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm flipV="1">
+          <a:off x="10833497" y="8524875"/>
+          <a:ext cx="716759" cy="642937"/>
+          <a:chOff x="10798969" y="7042547"/>
+          <a:chExt cx="714378" cy="642937"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="24" name="Straight Connector 23">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE46097D-C275-B9BB-FB5A-4B4787855AC9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10798969" y="7042547"/>
+            <a:ext cx="0" cy="631031"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="25" name="Straight Connector 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BCEF517-AEB2-BD81-7E9E-3A80522FCE52}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11507390" y="7054453"/>
+            <a:ext cx="0" cy="631031"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="26" name="Straight Connector 25">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{007E3068-0179-C289-CBC9-B2661F03F43A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10810875" y="7673579"/>
+            <a:ext cx="702472" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>577453</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>65485</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>567929</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>132160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Oval 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EC0A851-57D8-4D7E-AC5B-DC4DF6C49265}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6649641" y="7113985"/>
+          <a:ext cx="597694" cy="638175"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="tr-TR" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>577453</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>172640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>567929</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>48815</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="Oval 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26CD164E-A430-4274-B99E-1BF5A2326788}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6649641" y="8173640"/>
+          <a:ext cx="597694" cy="638175"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="tr-TR" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>35720</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>29765</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>313608</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>115003</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="Picture 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{861808C2-DE98-B192-6DAB-176F317AC236}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2464595" y="10126265"/>
+          <a:ext cx="5742857" cy="3895238"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>589360</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>29766</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>261938</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="TextBox 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB69CB08-A67E-C7FD-4AB9-084263DE6D0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7268766" y="12412266"/>
+          <a:ext cx="279797" cy="255984"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>B</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>47626</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>327423</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>136921</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="TextBox 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DE73E7E-6C67-434A-B235-4C0170E2DC8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4905376" y="10739437"/>
+          <a:ext cx="279797" cy="255984"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>306916</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>5953</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>273540</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>103120</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="Picture 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3281198A-DB97-0054-03E1-95DCD7D48883}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="8260504" y="10649928"/>
+          <a:ext cx="4097667" cy="3002717"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>101463</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>169277</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>208619</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>44261</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="TextBox 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA4B1350-7ED4-41BE-9EE4-A253F1EDBCC0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15424289" y="14075777"/>
+          <a:ext cx="720069" cy="255984"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>B = 6.00</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>172641</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>107156</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>279796</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>172640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="TextBox 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC0FC80B-A700-44A9-A6D7-F8A0B7A461A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9888141" y="13442156"/>
+          <a:ext cx="714374" cy="255984"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>D = 1.50</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>57978</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>57978</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>165134</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123462</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="TextBox 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F045F60-6F64-497C-BF23-433DD1CE9577}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11090413" y="11868978"/>
+          <a:ext cx="720069" cy="255984"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>B = 3.00</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>33130</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>140804</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>29741</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>93137</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Picture 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54A328B3-8487-9E9A-E7A7-F2EF567922DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11065565" y="12142304"/>
+          <a:ext cx="609524" cy="333333"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>8283</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>24848</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>4894</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>167681</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="41" name="Picture 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CB7C88E-FCC5-2C09-3558-8384CEF32996}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15331109" y="14502848"/>
+          <a:ext cx="609524" cy="333333"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>91109</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>182218</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>198265</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>57202</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="TextBox 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01135878-B53B-4378-94A4-2E89AAF7818C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14188109" y="16184218"/>
+          <a:ext cx="720069" cy="255984"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>D = 3.00</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>306456</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>57978</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>236400</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>105573</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="43" name="Picture 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13B8F3C8-ED78-113F-0CB6-175D00CA25EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14403456" y="15678978"/>
+          <a:ext cx="542857" cy="238095"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>215348</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>58116</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>204273</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>170929</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Picture 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B11B9B80-C300-3272-F44A-D53FE4C20C47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4505739" y="15107616"/>
+          <a:ext cx="4892230" cy="3541813"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>124239</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>74544</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>231395</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>140028</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="TextBox 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6FD217A-9E50-467D-8C36-5DC0EECCCE51}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13608326" y="12838044"/>
+          <a:ext cx="720069" cy="255984"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>t = 1.00</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>397565</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>33130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>546652</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>8282</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="58" name="Group 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D68DF510-E440-A151-E49C-4053E152B716}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="13808765" y="13177630"/>
+          <a:ext cx="149087" cy="165652"/>
+          <a:chOff x="13881652" y="13177630"/>
+          <a:chExt cx="149087" cy="165652"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="47" name="Straight Connector 46">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{502FBFCF-4F40-7AFD-3825-F710C3E41E62}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="13939630" y="13177630"/>
+            <a:ext cx="0" cy="149087"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="48" name="Straight Connector 47">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE730B73-2E34-42AB-AAB2-15834EA4DE6E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="13997609" y="13194195"/>
+            <a:ext cx="0" cy="149087"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="49" name="Straight Connector 48">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A350D22-DDA8-49F0-BEED-4026D67294DB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="5400000" flipV="1">
+            <a:off x="13956196" y="13152783"/>
+            <a:ext cx="0" cy="149087"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>463827</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>570983</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>65483</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="TextBox 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{038303B8-A8E4-4260-94B9-D85A14984463}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6592957" y="15620999"/>
+          <a:ext cx="720069" cy="255984"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>D = 3.00</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>604630</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>33130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>98873</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>98614</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="TextBox 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E507FA5-CBF4-4FB4-B28A-08F8E7AF1048}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8572500" y="16987630"/>
+          <a:ext cx="720069" cy="255984"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>B = 6.00</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>314740</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>132522</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>223631</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>132522</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="53" name="Straight Connector 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41FD5EDB-584E-2980-5B96-BF915BE22164}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="5830957" y="17087022"/>
+          <a:ext cx="521804" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>306457</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>49695</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>215348</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>49695</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="54" name="Straight Connector 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F7C82C0-546F-414F-BF47-6F4148AB1719}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="5822674" y="17194695"/>
+          <a:ext cx="521804" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>372718</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>107674</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>372718</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>66261</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="55" name="Straight Connector 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C43CF40B-10EA-43A0-A5E6-100A3DE7B38C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="5888935" y="17062174"/>
+          <a:ext cx="0" cy="149087"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>115957</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>24847</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>223113</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>90331</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="TextBox 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{296EE69D-F84A-4FF0-8ABB-95812F066990}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5019261" y="16979347"/>
+          <a:ext cx="720069" cy="255984"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>W = 3.00</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>240196</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>107674</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>347352</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>173158</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="57" name="TextBox 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97EC62F1-15E0-4A1C-BEFF-86198DD7E4EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7595153" y="18205174"/>
+          <a:ext cx="720069" cy="255984"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="1200">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>t = 1.50</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>33130</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>132522</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>182217</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>107674</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="59" name="Group 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AD43C78-2FFF-4BB4-AD6E-A050FA77A800}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="7348330" y="18230022"/>
+          <a:ext cx="149087" cy="165652"/>
+          <a:chOff x="13881652" y="13177630"/>
+          <a:chExt cx="149087" cy="165652"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="60" name="Straight Connector 59">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{775D689F-7BA3-2466-4914-CF7E775D6A87}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="13939630" y="13177630"/>
+            <a:ext cx="0" cy="149087"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="61" name="Straight Connector 60">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F46F2245-D3E7-750A-7AB7-58F58B7AE848}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="13997609" y="13194195"/>
+            <a:ext cx="0" cy="149087"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="62" name="Straight Connector 61">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB569D6F-5376-C6CA-3477-4478D5B2BC45}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm rot="5400000" flipV="1">
+            <a:off x="13956196" y="13152783"/>
+            <a:ext cx="0" cy="149087"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>298174</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>66261</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>510443</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>47166</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A6CBB43-60B8-15E3-F5FA-CAEA93F8736F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13169348" y="12258261"/>
+          <a:ext cx="1438095" cy="361905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>496957</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>49696</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>442560</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>2029</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Picture 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64855C9C-BAAA-BD5D-5E21-3EB3932B3EE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9077740" y="10336696"/>
+          <a:ext cx="1171429" cy="333333"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
